--- a/evals/datasets/document_extraction/files/DOC-119.xlsx
+++ b/evals/datasets/document_extraction/files/DOC-119.xlsx
@@ -413,41 +413,55 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Invoice INV-86884;2026-10-18;Material Clinico Levante S.L.</t>
+          <t>"Material Clinico Levante S.L.";"INVOICE";"INV-86884";"2026-10-18"</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Order;PO-0030;EUR</t>
+          <t>"Order";"PO-0030";"Currency";"EUR"</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>item;qty;unit_price;total</t>
+          <t>;;;</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VISOR;150;4.38;657.00</t>
+          <t>"Code";"Quantity";"Unit price";"Total"</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAP-BOUF;6;3.68;22.08</t>
+          <t>"VISOR";150;4.38;657.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>"CAP-BOUF";6;3.68;22.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>;;;"679.08"</t>
         </is>
       </c>
     </row>
